--- a/data/exports/news.xlsx
+++ b/data/exports/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>Google Research</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/03/qualcomm-backs-ultrahuman-in-70m-round-on-bet-to-turn-smart-rings-into-computers/</t>
+          <t>https://research.google/blog/transfer-learning-for-genomic-prediction-in-underrepresented-populations/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qualcomm backs Ultrahuman in $70M round on bet to turn smart rings into computers</t>
+          <t>Transfer learning for genomic prediction in underrepresented populations</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-04T17:02:26.915270+00:00</t>
+          <t>2026-09-04T17:02:30.460105+00:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/03/qualcomm-backs-ultrahuman-in-70m-round-on-bet-to-turn-smart-rings-into-computers/</t>
+          <t>https://research.google/blog/transfer-learning-for-genomic-prediction-in-underrepresented-populations/</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1328,81 +1328,11 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-03T17:00:00+00:00</t>
+          <t>2026-09-03T18:20:31+00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NEWS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Google Research</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://research.google/blog/transfer-learning-for-genomic-prediction-in-underrepresented-populations/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Transfer learning for genomic prediction in underrepresented populations</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-09-04T17:02:30.460105+00:00</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://research.google/blog/transfer-learning-for-genomic-prediction-in-underrepresented-populations/</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2026-09-03T18:20:31+00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
